--- a/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
+++ b/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="857"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="857" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="matriz_logica_simple" sheetId="7" r:id="rId1"/>
+    <sheet name="matriz_logica_simpleV1" sheetId="8" r:id="rId1"/>
+    <sheet name="matriz_logica_simple V2" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
   <si>
     <t>Perfil Calculado</t>
   </si>
@@ -189,6 +190,42 @@
   </si>
   <si>
     <t>Ahorro est. $50.0 - $120.0 USD/mes (66.6 - 160.0 kwh/mes)</t>
+  </si>
+  <si>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == True</t>
+  </si>
+  <si>
+    <t>(consumo_kwh / 30.0) &gt; 12.36 and horas_alto_consumo &gt; 6</t>
+  </si>
+  <si>
+    <t>(consumo_kwh / cantidad_equipos) &gt; 80.0</t>
+  </si>
+  <si>
+    <t>horas_alto_consumo &gt; 10</t>
+  </si>
+  <si>
+    <t>cantidad_equipos &gt;= 3 and (consumo_kwh / 30.0) &gt; 15.0</t>
+  </si>
+  <si>
+    <t>Comercio</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and horas_alto_consumo &gt; 10</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == True and horas_alto_consumo &gt; 8</t>
+  </si>
+  <si>
+    <t>horas_alto_consumo &gt; 12 and (consumo_kwh / cantidad_equipos) &gt; 60.0</t>
+  </si>
+  <si>
+    <t>superficie_m2 &gt; 0 and (consumo_kwh / superficie_m2) &gt; 22.76</t>
+  </si>
+  <si>
+    <t>Ineficiente</t>
   </si>
 </sst>
 </file>
@@ -795,4 +832,263 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
+++ b/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="matriz_logica_simpleV1" sheetId="8" r:id="rId1"/>
-    <sheet name="matriz_logica_simple V2" sheetId="7" r:id="rId2"/>
+    <sheet name="matriz_logica_simple V2" sheetId="9" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="85">
   <si>
     <t>Perfil Calculado</t>
   </si>
@@ -201,9 +201,6 @@
     <t>(consumo_kwh / 30.0) &gt; 12.36 and horas_alto_consumo &gt; 6</t>
   </si>
   <si>
-    <t>(consumo_kwh / cantidad_equipos) &gt; 80.0</t>
-  </si>
-  <si>
     <t>horas_alto_consumo &gt; 10</t>
   </si>
   <si>
@@ -226,6 +223,63 @@
   </si>
   <si>
     <t>Ineficiente</t>
+  </si>
+  <si>
+    <t>(consumo_kwh / cantidad_equipos) &gt; 40.0</t>
+  </si>
+  <si>
+    <t>Concentración de demanda en la hora pico</t>
+  </si>
+  <si>
+    <t>Reducir el uso de equipos durante los horarios pico</t>
+  </si>
+  <si>
+    <t>El consumo basal nocturno supera la línea base</t>
+  </si>
+  <si>
+    <t>Distribuir las actividades de mayor consumo a lo largo del día</t>
+  </si>
+  <si>
+    <t>Presencia de electrodomésticos de alta intensidad de consumo</t>
+  </si>
+  <si>
+    <t>Evaluar equipos con alto consumo energético</t>
+  </si>
+  <si>
+    <t>Uso prolongado de sistemas de climatización o alto consumo</t>
+  </si>
+  <si>
+    <t>Optimizar el tiempo de uso continuo de electrodomésticos</t>
+  </si>
+  <si>
+    <t>Consumo elevado por equipos térmicos o calentadores</t>
+  </si>
+  <si>
+    <t>Instalar temporizadores o ajustar la temperatura de calentadores</t>
+  </si>
+  <si>
+    <t>Alta simultaneidad de encendido en la apertura</t>
+  </si>
+  <si>
+    <t>Secuenciar el encendido de maquinaria y equipos en la apertura</t>
+  </si>
+  <si>
+    <t>Consumo residual elevado tras el cierre de operaciones</t>
+  </si>
+  <si>
+    <t>Implementar un protocolo de cierre y apagado de cargas nocturnas</t>
+  </si>
+  <si>
+    <t>Uso de tecnologías de iluminación o equipos ineficientes</t>
+  </si>
+  <si>
+    <t>Modernizar la iluminación a tecnología LED y reemplazar equipos obsoletos</t>
+  </si>
+  <si>
+    <t>Alta densidad de consumo por metro cuadrado</t>
+  </si>
+  <si>
+    <t>Realizar auditoría térmica y mejorar el aislamiento del establecimiento</t>
   </si>
 </sst>
 </file>
@@ -902,10 +956,10 @@
         <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>40</v>
@@ -919,10 +973,10 @@
         <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>41</v>
@@ -933,13 +987,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>42</v>
@@ -947,16 +1001,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>44</v>
@@ -964,16 +1018,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>45</v>
@@ -984,7 +1038,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1025,13 +1079,13 @@
         <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>47</v>
@@ -1042,13 +1096,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>48</v>
@@ -1056,16 +1110,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>49</v>
@@ -1073,16 +1127,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>54</v>

--- a/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
+++ b/data_simple_Team_72_EnergiAI/Matriz_Logica__Simple_EnergiAI_Teams_72.xlsx
@@ -9,11 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="857" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="857" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="matriz_logica_simpleV1" sheetId="8" r:id="rId1"/>
     <sheet name="matriz_logica_simple V2" sheetId="9" r:id="rId2"/>
+    <sheet name="matriz_logica_simple V3" sheetId="10" r:id="rId3"/>
+    <sheet name="matriz_logica_simple V4" sheetId="13" r:id="rId4"/>
+    <sheet name="matriz_logica_simple V5" sheetId="12" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,8 +27,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>SAMI</author>
+  </authors>
+  <commentList>
+    <comment ref="A26" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Con area</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sin area</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="121">
   <si>
     <t>Perfil Calculado</t>
   </si>
@@ -280,13 +341,121 @@
   </si>
   <si>
     <t>Realizar auditoría térmica y mejorar el aislamiento del establecimiento</t>
+  </si>
+  <si>
+    <t>Uso de potencia en bloques tarifarios altos</t>
+  </si>
+  <si>
+    <t>horas_alto_consumo &gt; 6</t>
+  </si>
+  <si>
+    <t>Consumo residual elevado o jornadas operativas extensas</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == True and horas_alto_consumo &lt;= 8</t>
+  </si>
+  <si>
+    <t>horas_alto_consumo &lt;= 10 and (consumo_kwh / cantidad_equipos) &gt; 30.0</t>
+  </si>
+  <si>
+    <t>Impacto financiero esperado $0.75/kWh (Ahorro est. $ (consumo_kwh * 0.75 * %_eficiencia)</t>
+  </si>
+  <si>
+    <t>% Eficiencia (Ahorro)</t>
+  </si>
+  <si>
+    <t>Criterio Técnico Ahorro</t>
+  </si>
+  <si>
+    <t>Desplazamiento de carga intensiva a bloques no fraccionados / tarifarios bajos.</t>
+  </si>
+  <si>
+    <t>Optimización del perfil de uso diario y nivelación del consumo basal.</t>
+  </si>
+  <si>
+    <t>Detección de electrodomésticos ineficientes o con fugas de rendimiento.</t>
+  </si>
+  <si>
+    <t>Control de tiempo activo en sistemas de climatización o refrigeración.</t>
+  </si>
+  <si>
+    <t>Reducción de pérdidas térmicas directas y control automático de encendido.</t>
+  </si>
+  <si>
+    <t>Evita cobros por exceso de demanda en horas de alta tarifa comercial.</t>
+  </si>
+  <si>
+    <t>Eliminación del consumo residual "vampiro" fuera del horario operativo.</t>
+  </si>
+  <si>
+    <t>Mitigación de picos de arranque de potencia durante la apertura del local.</t>
+  </si>
+  <si>
+    <t>Eliminación de cargas fantasmas tras el cierre del establecimiento.</t>
+  </si>
+  <si>
+    <t>Salto tecnológico directo en iluminación y equipos de trabajo continuo.</t>
+  </si>
+  <si>
+    <t>Reducción de la carga térmica sobre aire acondicionado y climatización.</t>
+  </si>
+  <si>
+    <t>Gestión de demanda puntual en bloques tarifarios altos.</t>
+  </si>
+  <si>
+    <t>Control de cargas remanentes en jornadas moderadas.</t>
+  </si>
+  <si>
+    <t>consumo_kwh * 0.75 * 0.15</t>
+  </si>
+  <si>
+    <t>consumo_kwh * 0.75 * 0.08</t>
+  </si>
+  <si>
+    <t>consumo_kwh * 0.75 * 0.10</t>
+  </si>
+  <si>
+    <t>consumo_kwh * 0.75 * 0.12</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and 6 &lt; horas_alto_consumo &lt;= 10</t>
+  </si>
+  <si>
+    <t>horas_alto_consumo &lt;= 6 and (consumo_kwh / cantidad_equipos) &gt; 30.0</t>
+  </si>
+  <si>
+    <t>Eficiente</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and (consumo_kwh / 30.0) &lt;= 9.21</t>
+  </si>
+  <si>
+    <t>Desempeño óptimo y hábitos energéticos sostenibles</t>
+  </si>
+  <si>
+    <t>Mantener hábitos de consumo actuales. No se detectan ineficiencias o fugas energéticas.</t>
+  </si>
+  <si>
+    <t>consumo_kwh * 0.75 * 0</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and (consumo_kwh / superficie_m2) &lt;= 12.87</t>
+  </si>
+  <si>
+    <t>Consumo optimizado</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and superficie_m2 &gt; 0 and (consumo_kwh / superficie_m2) &lt;= 12.87</t>
+  </si>
+  <si>
+    <t>uso_horario_pico == False and superficie_m2 == 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +470,39 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -341,19 +543,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1145,4 +1352,1337 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>